--- a/Assets/Resources/Data/GameData.xlsx
+++ b/Assets/Resources/Data/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\GreedDungeon\Assets\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65460E4A-ABD2-40BE-856B-C0CED5C434B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D740A844-41C6-4B8E-ADA2-8EADE63B8C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{0D21060C-878B-4774-A478-36615BE855B3}"/>
+    <workbookView xWindow="4380" yWindow="2040" windowWidth="21600" windowHeight="11385" xr2:uid="{0D21060C-878B-4774-A478-36615BE855B3}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="112">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,10 +108,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Brun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Poison</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -152,10 +148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>accessories</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>StatMultiplier</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -212,10 +204,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Fasle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MPCost</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -256,10 +244,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>골렘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>좀비</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -400,10 +384,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Dagame</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Single</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -493,6 +473,17 @@
   </si>
   <si>
     <t>Max%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골렘(불)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>Damage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,10 +909,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D2">
         <v>40</v>
@@ -953,8 +944,8 @@
       <c r="M2" t="s">
         <v>15</v>
       </c>
-      <c r="N2" t="s">
-        <v>43</v>
+      <c r="N2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -962,10 +953,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -989,7 +980,7 @@
         <v>45</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="L3">
         <v>20</v>
@@ -997,8 +988,8 @@
       <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="N3" t="s">
-        <v>43</v>
+      <c r="N3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1006,10 +997,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -1033,7 +1024,7 @@
         <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L4">
         <v>30</v>
@@ -1041,8 +1032,8 @@
       <c r="M4" t="s">
         <v>15</v>
       </c>
-      <c r="N4" t="s">
-        <v>43</v>
+      <c r="N4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1050,10 +1041,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
         <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1077,7 +1068,7 @@
         <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1085,8 +1076,8 @@
       <c r="M5" t="s">
         <v>15</v>
       </c>
-      <c r="N5" t="s">
-        <v>43</v>
+      <c r="N5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1094,10 +1085,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>500</v>
@@ -1161,13 +1152,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1182,13 +1173,13 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>24</v>
-      </c>
-      <c r="L1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -1196,10 +1187,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1220,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K2">
         <v>50</v>
@@ -1234,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1258,7 +1249,7 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K3">
         <v>200</v>
@@ -1272,10 +1263,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>20</v>
@@ -1296,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K4">
         <v>180</v>
@@ -1310,10 +1301,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1334,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K5">
         <v>250</v>
@@ -1348,10 +1339,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1372,7 +1363,7 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K6">
         <v>220</v>
@@ -1386,10 +1377,10 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>15</v>
@@ -1410,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K7">
         <v>150</v>
@@ -1424,10 +1415,10 @@
         <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8">
         <v>30</v>
@@ -1448,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K8">
         <v>300</v>
@@ -1462,10 +1453,10 @@
         <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -1486,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K9">
         <v>550</v>
@@ -1500,10 +1491,10 @@
         <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>20</v>
@@ -1524,7 +1515,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K10">
         <v>400</v>
@@ -1538,10 +1529,10 @@
         <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1562,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K11">
         <v>350</v>
@@ -1576,10 +1567,10 @@
         <v>201</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1600,7 +1591,7 @@
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K12">
         <v>150</v>
@@ -1614,10 +1605,10 @@
         <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1638,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K13">
         <v>200</v>
@@ -1652,10 +1643,10 @@
         <v>203</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1676,7 +1667,7 @@
         <v>2</v>
       </c>
       <c r="J14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K14">
         <v>180</v>
@@ -1690,10 +1681,10 @@
         <v>204</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1714,7 +1705,7 @@
         <v>10</v>
       </c>
       <c r="J15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K15">
         <v>250</v>
@@ -1728,10 +1719,10 @@
         <v>205</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1752,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K16">
         <v>220</v>
@@ -1788,19 +1779,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1808,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1831,7 +1822,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>1.1000000000000001</v>
@@ -1854,7 +1845,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>1.25</v>
@@ -1877,7 +1868,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>1.5</v>
@@ -1900,7 +1891,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1949,25 +1940,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>46</v>
-      </c>
-      <c r="G1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" t="s">
-        <v>49</v>
       </c>
       <c r="J1" t="s">
         <v>10</v>
@@ -1976,7 +1967,7 @@
         <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -1984,19 +1975,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G2">
         <v>1.2</v>
@@ -2005,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -2022,19 +2013,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G3">
         <v>0.8</v>
@@ -2043,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J3" t="s">
         <v>14</v>
@@ -2060,19 +2051,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G4">
         <v>0.7</v>
@@ -2081,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
@@ -2098,19 +2089,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G5">
         <v>2.2000000000000002</v>
@@ -2119,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s">
         <v>14</v>
@@ -2136,19 +2127,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G6">
         <v>1.3</v>
@@ -2157,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
@@ -2174,19 +2165,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G7">
         <v>1.8</v>
@@ -2195,10 +2186,10 @@
         <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K7">
         <v>50</v>
@@ -2212,19 +2203,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G8">
         <v>1.5</v>
@@ -2233,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -2250,19 +2241,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -2271,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J9" t="s">
         <v>14</v>
@@ -2288,19 +2279,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -2309,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
@@ -2326,19 +2317,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G11">
         <v>20</v>
@@ -2347,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J11" t="s">
         <v>14</v>
@@ -2364,19 +2355,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -2385,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
@@ -2402,19 +2393,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G13">
         <v>1.3</v>
@@ -2423,7 +2414,7 @@
         <v>3</v>
       </c>
       <c r="I13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
@@ -2440,19 +2431,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D14">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G14">
         <v>1.4</v>
@@ -2461,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="I14" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
@@ -2478,19 +2469,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D15">
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -2499,7 +2490,7 @@
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J15" t="s">
         <v>14</v>
@@ -2516,19 +2507,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G16">
         <v>1.25</v>
@@ -2537,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
@@ -2571,19 +2562,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -2591,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2614,7 +2605,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2637,7 +2628,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>0</v>
